--- a/CONTROL_VERSIONES.xlsx
+++ b/CONTROL_VERSIONES.xlsx
@@ -1,133 +1,71 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JPCS1\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
-  <si>
-    <t>Versión</t>
-  </si>
-  <si>
-    <t>Fecha</t>
-  </si>
-  <si>
-    <t>Tipo de objeto</t>
-  </si>
-  <si>
-    <t>Descripción</t>
-  </si>
-  <si>
-    <t>José Carbajal</t>
-  </si>
-  <si>
-    <t>Responsable</t>
-  </si>
-  <si>
-    <t>Rol</t>
-  </si>
-  <si>
-    <t>Operación SQL</t>
-  </si>
-  <si>
-    <t>Objeto</t>
-  </si>
-  <si>
-    <t>DBA</t>
-  </si>
-  <si>
-    <t>CREATE DATABASE</t>
-  </si>
-  <si>
-    <t>control_escolar</t>
-  </si>
-  <si>
-    <t>PROC_SP_ALUMNOS</t>
-  </si>
-  <si>
-    <t>SI</t>
-  </si>
-  <si>
-    <t>Base de Datos</t>
-  </si>
-  <si>
-    <t>Creación de la base de datos del sistema de control escolar</t>
-  </si>
-  <si>
-    <t>CREATE PROCEDURE</t>
-  </si>
-  <si>
-    <t>Procedimiento almacenado</t>
-  </si>
-  <si>
-    <t>Procedimiento almacenado para gestionar alumnos</t>
-  </si>
-  <si>
-    <t>USUARIOS</t>
-  </si>
-  <si>
-    <t>APROBADO</t>
-  </si>
-  <si>
-    <t>ROL</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
+  </numFmts>
+  <fonts count="7">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="18"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="18"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001B5E20"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -138,8 +76,23 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000D2B6E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -382,100 +335,209 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0BEC5"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0BEC5"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0BEC5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0BEC5"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+  <cellXfs count="41">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -741,226 +803,3370 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:K17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K74"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="18.6640625" customWidth="1"/>
-    <col min="8" max="8" width="27.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="22" customWidth="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="18" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="70" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="J2" s="24" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="2:11" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="19">
-        <v>1</v>
-      </c>
-      <c r="C3" s="20">
-        <v>46090</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="K3" s="23"/>
-    </row>
-    <row r="4" spans="2:11" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="19">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="C4" s="20">
-        <v>46091</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="28" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B5" s="12"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="25"/>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B6" s="5"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="25"/>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B7" s="7"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="25"/>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B8" s="7"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="25"/>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B9" s="7"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="25"/>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="25"/>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B11" s="7"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="25"/>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B12" s="7"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="25"/>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B13" s="7"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="25"/>
-    </row>
-    <row r="14" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="9"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="26"/>
-    </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C17" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" t="s">
-        <v>21</v>
+    <row r="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>Versión</t>
+        </is>
+      </c>
+      <c r="B1" s="29" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="C1" s="29" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="D1" s="29" t="inlineStr">
+        <is>
+          <t>Rol</t>
+        </is>
+      </c>
+      <c r="E1" s="29" t="inlineStr">
+        <is>
+          <t>Operación SQL</t>
+        </is>
+      </c>
+      <c r="F1" s="29" t="inlineStr">
+        <is>
+          <t>Tipo de objeto</t>
+        </is>
+      </c>
+      <c r="G1" s="29" t="inlineStr">
+        <is>
+          <t>Objeto</t>
+        </is>
+      </c>
+      <c r="H1" s="29" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="I1" s="29" t="inlineStr">
+        <is>
+          <t>APROBADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1" thickBot="1">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="B2" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C2" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D2" s="30" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E2" s="30" t="inlineStr">
+        <is>
+          <t>CREATE DATABASE</t>
+        </is>
+      </c>
+      <c r="F2" s="30" t="inlineStr">
+        <is>
+          <t>Base de Datos</t>
+        </is>
+      </c>
+      <c r="G2" s="30" t="inlineStr">
+        <is>
+          <t>control_escolar_n</t>
+        </is>
+      </c>
+      <c r="H2" s="32" t="inlineStr">
+        <is>
+          <t>Creación de la base de datos principal del sistema de control escolar</t>
+        </is>
+      </c>
+      <c r="I2" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J2" s="24" t="n"/>
+    </row>
+    <row r="3" ht="28" customHeight="1" thickBot="1">
+      <c r="A3" s="34" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B3" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C3" s="36" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D3" s="34" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E3" s="34" t="inlineStr">
+        <is>
+          <t>CREATE TABLE</t>
+        </is>
+      </c>
+      <c r="F3" s="34" t="inlineStr">
+        <is>
+          <t>Tabla</t>
+        </is>
+      </c>
+      <c r="G3" s="34" t="inlineStr">
+        <is>
+          <t>carrera</t>
+        </is>
+      </c>
+      <c r="H3" s="37" t="inlineStr">
+        <is>
+          <t>Tabla de carreras académicas (Ing. Sistemas / Industrial)</t>
+        </is>
+      </c>
+      <c r="I3" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J3" s="27" t="n"/>
+      <c r="K3" s="23" t="n"/>
+    </row>
+    <row r="4" ht="28" customHeight="1" thickBot="1">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B4" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C4" s="38" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D4" s="30" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E4" s="30" t="inlineStr">
+        <is>
+          <t>CREATE TABLE</t>
+        </is>
+      </c>
+      <c r="F4" s="30" t="inlineStr">
+        <is>
+          <t>Tabla</t>
+        </is>
+      </c>
+      <c r="G4" s="30" t="inlineStr">
+        <is>
+          <t>grupo</t>
+        </is>
+      </c>
+      <c r="H4" s="32" t="inlineStr">
+        <is>
+          <t>Tabla de grupos por carrera y grado (5A, 6B, etc.)</t>
+        </is>
+      </c>
+      <c r="I4" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="n"/>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B5" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D5" s="34" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E5" s="34" t="inlineStr">
+        <is>
+          <t>CREATE TABLE</t>
+        </is>
+      </c>
+      <c r="F5" s="34" t="inlineStr">
+        <is>
+          <t>Tabla</t>
+        </is>
+      </c>
+      <c r="G5" s="34" t="inlineStr">
+        <is>
+          <t>materia</t>
+        </is>
+      </c>
+      <c r="H5" s="37" t="inlineStr">
+        <is>
+          <t>Tabla de materias con clave y créditos (48 materias, Sistemas e Industrial)</t>
+        </is>
+      </c>
+      <c r="I5" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="B6" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C6" s="38" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D6" s="30" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E6" s="30" t="inlineStr">
+        <is>
+          <t>CREATE TABLE</t>
+        </is>
+      </c>
+      <c r="F6" s="30" t="inlineStr">
+        <is>
+          <t>Tabla</t>
+        </is>
+      </c>
+      <c r="G6" s="30" t="inlineStr">
+        <is>
+          <t>periodo</t>
+        </is>
+      </c>
+      <c r="H6" s="32" t="inlineStr">
+        <is>
+          <t>Tabla de periodos escolares con fechas de inicio y fin</t>
+        </is>
+      </c>
+      <c r="I6" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J6" s="25" t="n"/>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="34" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="B7" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C7" s="36" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D7" s="34" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E7" s="34" t="inlineStr">
+        <is>
+          <t>CREATE TABLE</t>
+        </is>
+      </c>
+      <c r="F7" s="34" t="inlineStr">
+        <is>
+          <t>Tabla</t>
+        </is>
+      </c>
+      <c r="G7" s="34" t="inlineStr">
+        <is>
+          <t>docente</t>
+        </is>
+      </c>
+      <c r="H7" s="37" t="inlineStr">
+        <is>
+          <t>Tabla de docentes con nombre y correo</t>
+        </is>
+      </c>
+      <c r="I7" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J7" s="25" t="n"/>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="B8" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C8" s="38" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D8" s="30" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E8" s="30" t="inlineStr">
+        <is>
+          <t>CREATE TABLE</t>
+        </is>
+      </c>
+      <c r="F8" s="30" t="inlineStr">
+        <is>
+          <t>Tabla</t>
+        </is>
+      </c>
+      <c r="G8" s="30" t="inlineStr">
+        <is>
+          <t>alumno</t>
+        </is>
+      </c>
+      <c r="H8" s="32" t="inlineStr">
+        <is>
+          <t>Tabla de alumnos con matrícula autogenerada y relación a grupo</t>
+        </is>
+      </c>
+      <c r="I8" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J8" s="25" t="n"/>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="34" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="B9" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C9" s="36" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D9" s="34" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E9" s="34" t="inlineStr">
+        <is>
+          <t>CREATE TABLE</t>
+        </is>
+      </c>
+      <c r="F9" s="34" t="inlineStr">
+        <is>
+          <t>Tabla</t>
+        </is>
+      </c>
+      <c r="G9" s="34" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+      <c r="H9" s="37" t="inlineStr">
+        <is>
+          <t>Tabla de usuarios del sistema con rol (control, docente, alumno)</t>
+        </is>
+      </c>
+      <c r="I9" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J9" s="25" t="n"/>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="30" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="B10" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C10" s="38" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D10" s="30" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E10" s="30" t="inlineStr">
+        <is>
+          <t>CREATE TABLE</t>
+        </is>
+      </c>
+      <c r="F10" s="30" t="inlineStr">
+        <is>
+          <t>Tabla</t>
+        </is>
+      </c>
+      <c r="G10" s="30" t="inlineStr">
+        <is>
+          <t>asignacion</t>
+        </is>
+      </c>
+      <c r="H10" s="32" t="inlineStr">
+        <is>
+          <t>Tabla de asignaciones docente-materia-grupo-periodo con restricción de unicidad</t>
+        </is>
+      </c>
+      <c r="I10" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J10" s="25" t="n"/>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="34" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="B11" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C11" s="36" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D11" s="34" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E11" s="34" t="inlineStr">
+        <is>
+          <t>CREATE TABLE</t>
+        </is>
+      </c>
+      <c r="F11" s="34" t="inlineStr">
+        <is>
+          <t>Tabla</t>
+        </is>
+      </c>
+      <c r="G11" s="34" t="inlineStr">
+        <is>
+          <t>inscripcion</t>
+        </is>
+      </c>
+      <c r="H11" s="37" t="inlineStr">
+        <is>
+          <t>Tabla de inscripciones alumno-asignación con fecha automática</t>
+        </is>
+      </c>
+      <c r="I11" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="n"/>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="30" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="B12" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C12" s="38" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D12" s="30" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E12" s="30" t="inlineStr">
+        <is>
+          <t>CREATE TABLE</t>
+        </is>
+      </c>
+      <c r="F12" s="30" t="inlineStr">
+        <is>
+          <t>Tabla</t>
+        </is>
+      </c>
+      <c r="G12" s="30" t="inlineStr">
+        <is>
+          <t>calificacion</t>
+        </is>
+      </c>
+      <c r="H12" s="32" t="inlineStr">
+        <is>
+          <t>Tabla de calificaciones (3 parciales + 3 asistencias) por inscripción</t>
+        </is>
+      </c>
+      <c r="I12" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J12" s="25" t="n"/>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="34" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="B13" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C13" s="36" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D13" s="34" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E13" s="34" t="inlineStr">
+        <is>
+          <t>CREATE TABLE</t>
+        </is>
+      </c>
+      <c r="F13" s="34" t="inlineStr">
+        <is>
+          <t>Tabla</t>
+        </is>
+      </c>
+      <c r="G13" s="34" t="inlineStr">
+        <is>
+          <t>auditoria</t>
+        </is>
+      </c>
+      <c r="H13" s="37" t="inlineStr">
+        <is>
+          <t>Tabla de auditoría para registro de todos los eventos del sistema (INSERT/UPDATE/DELETE/LOGIN/LOGOUT)</t>
+        </is>
+      </c>
+      <c r="I13" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1" thickBot="1">
+      <c r="A14" s="30" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="B14" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C14" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D14" s="30" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E14" s="30" t="inlineStr">
+        <is>
+          <t>CREATE VIEW</t>
+        </is>
+      </c>
+      <c r="F14" s="30" t="inlineStr">
+        <is>
+          <t>Vista</t>
+        </is>
+      </c>
+      <c r="G14" s="30" t="inlineStr">
+        <is>
+          <t>v_auditoria</t>
+        </is>
+      </c>
+      <c r="H14" s="32" t="inlineStr">
+        <is>
+          <t>Vista de auditoría ordenada por fecha descendente para consulta rápida de eventos</t>
+        </is>
+      </c>
+      <c r="I14" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J14" s="26" t="n"/>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="34" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="B15" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C15" s="34" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D15" s="34" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E15" s="34" t="inlineStr">
+        <is>
+          <t>CREATE PROCEDURE</t>
+        </is>
+      </c>
+      <c r="F15" s="34" t="inlineStr">
+        <is>
+          <t>Procedimiento almacenado</t>
+        </is>
+      </c>
+      <c r="G15" s="34" t="inlineStr">
+        <is>
+          <t>sp_aud_sesion</t>
+        </is>
+      </c>
+      <c r="H15" s="37" t="inlineStr">
+        <is>
+          <t>Procedimiento para registrar eventos de LOGIN/LOGOUT en la tabla auditoria</t>
+        </is>
+      </c>
+      <c r="I15" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="30" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="B16" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C16" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D16" s="30" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E16" s="30" t="inlineStr">
+        <is>
+          <t>CREATE PROCEDURE</t>
+        </is>
+      </c>
+      <c r="F16" s="30" t="inlineStr">
+        <is>
+          <t>Procedimiento almacenado</t>
+        </is>
+      </c>
+      <c r="G16" s="30" t="inlineStr">
+        <is>
+          <t>sp_crear_usuario_alumno</t>
+        </is>
+      </c>
+      <c r="H16" s="32" t="inlineStr">
+        <is>
+          <t>Procedimiento para crear usuario de tipo alumno a partir del idAlumno y contraseña</t>
+        </is>
+      </c>
+      <c r="I16" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="34" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="B17" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C17" s="34" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D17" s="34" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E17" s="34" t="inlineStr">
+        <is>
+          <t>CREATE PROCEDURE</t>
+        </is>
+      </c>
+      <c r="F17" s="34" t="inlineStr">
+        <is>
+          <t>Procedimiento almacenado</t>
+        </is>
+      </c>
+      <c r="G17" s="34" t="inlineStr">
+        <is>
+          <t>sp_crear_usuario_docente</t>
+        </is>
+      </c>
+      <c r="H17" s="37" t="inlineStr">
+        <is>
+          <t>Procedimiento para crear usuario de tipo docente a partir del idDocente y contraseña</t>
+        </is>
+      </c>
+      <c r="I17" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="30" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="B18" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C18" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D18" s="30" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E18" s="30" t="inlineStr">
+        <is>
+          <t>CREATE PROCEDURE</t>
+        </is>
+      </c>
+      <c r="F18" s="30" t="inlineStr">
+        <is>
+          <t>Procedimiento almacenado</t>
+        </is>
+      </c>
+      <c r="G18" s="30" t="inlineStr">
+        <is>
+          <t>sp_inscribir_alumno</t>
+        </is>
+      </c>
+      <c r="H18" s="32" t="inlineStr">
+        <is>
+          <t>Procedimiento para inscribir un alumno a una asignación validando duplicados</t>
+        </is>
+      </c>
+      <c r="I18" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="34" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="B19" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C19" s="34" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D19" s="34" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E19" s="34" t="inlineStr">
+        <is>
+          <t>CREATE PROCEDURE</t>
+        </is>
+      </c>
+      <c r="F19" s="34" t="inlineStr">
+        <is>
+          <t>Procedimiento almacenado</t>
+        </is>
+      </c>
+      <c r="G19" s="34" t="inlineStr">
+        <is>
+          <t>sp_registrar_calificacion</t>
+        </is>
+      </c>
+      <c r="H19" s="37" t="inlineStr">
+        <is>
+          <t>Procedimiento para insertar o actualizar calificaciones de una inscripción</t>
+        </is>
+      </c>
+      <c r="I19" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="B20" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C20" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D20" s="30" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E20" s="30" t="inlineStr">
+        <is>
+          <t>CREATE TRIGGER</t>
+        </is>
+      </c>
+      <c r="F20" s="30" t="inlineStr">
+        <is>
+          <t>Disparador</t>
+        </is>
+      </c>
+      <c r="G20" s="30" t="inlineStr">
+        <is>
+          <t>trg_check_matricula</t>
+        </is>
+      </c>
+      <c r="H20" s="32" t="inlineStr">
+        <is>
+          <t>Trigger BEFORE INSERT en alumno: valida que la matrícula no exista previamente</t>
+        </is>
+      </c>
+      <c r="I20" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="34" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="B21" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C21" s="34" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D21" s="34" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E21" s="34" t="inlineStr">
+        <is>
+          <t>CREATE TRIGGER</t>
+        </is>
+      </c>
+      <c r="F21" s="34" t="inlineStr">
+        <is>
+          <t>Disparador</t>
+        </is>
+      </c>
+      <c r="G21" s="34" t="inlineStr">
+        <is>
+          <t>trg_usuario_alumno</t>
+        </is>
+      </c>
+      <c r="H21" s="37" t="inlineStr">
+        <is>
+          <t>Trigger AFTER INSERT en alumno: crea usuario con rol alumno e inscribe en asignaciones del grupo</t>
+        </is>
+      </c>
+      <c r="I21" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="B22" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C22" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D22" s="30" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E22" s="30" t="inlineStr">
+        <is>
+          <t>CREATE TRIGGER</t>
+        </is>
+      </c>
+      <c r="F22" s="30" t="inlineStr">
+        <is>
+          <t>Disparador</t>
+        </is>
+      </c>
+      <c r="G22" s="30" t="inlineStr">
+        <is>
+          <t>trg_aud_alumno_insert</t>
+        </is>
+      </c>
+      <c r="H22" s="32" t="inlineStr">
+        <is>
+          <t>Trigger AFTER INSERT en alumno: registra el evento en la tabla auditoria (severidad: info)</t>
+        </is>
+      </c>
+      <c r="I22" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="34" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="B23" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C23" s="34" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D23" s="34" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E23" s="34" t="inlineStr">
+        <is>
+          <t>CREATE TRIGGER</t>
+        </is>
+      </c>
+      <c r="F23" s="34" t="inlineStr">
+        <is>
+          <t>Disparador</t>
+        </is>
+      </c>
+      <c r="G23" s="34" t="inlineStr">
+        <is>
+          <t>trg_aud_alumno_update</t>
+        </is>
+      </c>
+      <c r="H23" s="37" t="inlineStr">
+        <is>
+          <t>Trigger AFTER UPDATE en alumno: registra cambios en auditoria (severidad: advertencia)</t>
+        </is>
+      </c>
+      <c r="I23" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="30" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="B24" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C24" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D24" s="30" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E24" s="30" t="inlineStr">
+        <is>
+          <t>CREATE TRIGGER</t>
+        </is>
+      </c>
+      <c r="F24" s="30" t="inlineStr">
+        <is>
+          <t>Disparador</t>
+        </is>
+      </c>
+      <c r="G24" s="30" t="inlineStr">
+        <is>
+          <t>trg_update_inscripcion_alumno</t>
+        </is>
+      </c>
+      <c r="H24" s="32" t="inlineStr">
+        <is>
+          <t>Trigger AFTER UPDATE en alumno: reasigna inscripciones si cambia de grupo</t>
+        </is>
+      </c>
+      <c r="I24" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="34" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="B25" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C25" s="34" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D25" s="34" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E25" s="34" t="inlineStr">
+        <is>
+          <t>CREATE TRIGGER</t>
+        </is>
+      </c>
+      <c r="F25" s="34" t="inlineStr">
+        <is>
+          <t>Disparador</t>
+        </is>
+      </c>
+      <c r="G25" s="34" t="inlineStr">
+        <is>
+          <t>trg_update_usuario_alumno</t>
+        </is>
+      </c>
+      <c r="H25" s="37" t="inlineStr">
+        <is>
+          <t>Trigger AFTER UPDATE en alumno: sincroniza correo en tabla usuario</t>
+        </is>
+      </c>
+      <c r="I25" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="B26" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C26" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D26" s="30" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E26" s="30" t="inlineStr">
+        <is>
+          <t>CREATE TRIGGER</t>
+        </is>
+      </c>
+      <c r="F26" s="30" t="inlineStr">
+        <is>
+          <t>Disparador</t>
+        </is>
+      </c>
+      <c r="G26" s="30" t="inlineStr">
+        <is>
+          <t>trg_aud_alumno_delete</t>
+        </is>
+      </c>
+      <c r="H26" s="32" t="inlineStr">
+        <is>
+          <t>Trigger AFTER DELETE en alumno: registra eliminación en auditoria (severidad: crítico)</t>
+        </is>
+      </c>
+      <c r="I26" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="34" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="B27" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C27" s="34" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D27" s="34" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E27" s="34" t="inlineStr">
+        <is>
+          <t>CREATE TRIGGER</t>
+        </is>
+      </c>
+      <c r="F27" s="34" t="inlineStr">
+        <is>
+          <t>Disparador</t>
+        </is>
+      </c>
+      <c r="G27" s="34" t="inlineStr">
+        <is>
+          <t>trg_delete_usuario_alumno</t>
+        </is>
+      </c>
+      <c r="H27" s="37" t="inlineStr">
+        <is>
+          <t>Trigger AFTER DELETE en alumno: elimina el usuario asociado en cascada</t>
+        </is>
+      </c>
+      <c r="I27" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="B28" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C28" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D28" s="30" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E28" s="30" t="inlineStr">
+        <is>
+          <t>CREATE TRIGGER</t>
+        </is>
+      </c>
+      <c r="F28" s="30" t="inlineStr">
+        <is>
+          <t>Disparador</t>
+        </is>
+      </c>
+      <c r="G28" s="30" t="inlineStr">
+        <is>
+          <t>trg_usuario_docente</t>
+        </is>
+      </c>
+      <c r="H28" s="32" t="inlineStr">
+        <is>
+          <t>Trigger AFTER INSERT en docente: crea usuario con rol docente automáticamente</t>
+        </is>
+      </c>
+      <c r="I28" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="34" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="B29" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C29" s="34" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D29" s="34" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E29" s="34" t="inlineStr">
+        <is>
+          <t>CREATE TRIGGER</t>
+        </is>
+      </c>
+      <c r="F29" s="34" t="inlineStr">
+        <is>
+          <t>Disparador</t>
+        </is>
+      </c>
+      <c r="G29" s="34" t="inlineStr">
+        <is>
+          <t>trg_aud_docente_insert</t>
+        </is>
+      </c>
+      <c r="H29" s="37" t="inlineStr">
+        <is>
+          <t>Trigger AFTER INSERT en docente: registra en auditoria (severidad: info)</t>
+        </is>
+      </c>
+      <c r="I29" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="30" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="B30" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C30" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D30" s="30" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E30" s="30" t="inlineStr">
+        <is>
+          <t>CREATE TRIGGER</t>
+        </is>
+      </c>
+      <c r="F30" s="30" t="inlineStr">
+        <is>
+          <t>Disparador</t>
+        </is>
+      </c>
+      <c r="G30" s="30" t="inlineStr">
+        <is>
+          <t>trg_aud_docente_update</t>
+        </is>
+      </c>
+      <c r="H30" s="32" t="inlineStr">
+        <is>
+          <t>Trigger AFTER UPDATE en docente: registra cambios en auditoria (severidad: advertencia)</t>
+        </is>
+      </c>
+      <c r="I30" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="34" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="B31" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C31" s="34" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D31" s="34" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E31" s="34" t="inlineStr">
+        <is>
+          <t>CREATE TRIGGER</t>
+        </is>
+      </c>
+      <c r="F31" s="34" t="inlineStr">
+        <is>
+          <t>Disparador</t>
+        </is>
+      </c>
+      <c r="G31" s="34" t="inlineStr">
+        <is>
+          <t>trg_update_usuario_docente</t>
+        </is>
+      </c>
+      <c r="H31" s="37" t="inlineStr">
+        <is>
+          <t>Trigger AFTER UPDATE en docente: sincroniza nombre y correo en tabla usuario</t>
+        </is>
+      </c>
+      <c r="I31" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="30" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="B32" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C32" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D32" s="30" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E32" s="30" t="inlineStr">
+        <is>
+          <t>CREATE TRIGGER</t>
+        </is>
+      </c>
+      <c r="F32" s="30" t="inlineStr">
+        <is>
+          <t>Disparador</t>
+        </is>
+      </c>
+      <c r="G32" s="30" t="inlineStr">
+        <is>
+          <t>trg_aud_docente_delete</t>
+        </is>
+      </c>
+      <c r="H32" s="32" t="inlineStr">
+        <is>
+          <t>Trigger AFTER DELETE en docente: registra en auditoria (severidad: crítico)</t>
+        </is>
+      </c>
+      <c r="I32" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="34" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="B33" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C33" s="34" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D33" s="34" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E33" s="34" t="inlineStr">
+        <is>
+          <t>CREATE TRIGGER</t>
+        </is>
+      </c>
+      <c r="F33" s="34" t="inlineStr">
+        <is>
+          <t>Disparador</t>
+        </is>
+      </c>
+      <c r="G33" s="34" t="inlineStr">
+        <is>
+          <t>trg_delete_usuario_docente</t>
+        </is>
+      </c>
+      <c r="H33" s="37" t="inlineStr">
+        <is>
+          <t>Trigger AFTER DELETE en docente: elimina usuario asociado en cascada</t>
+        </is>
+      </c>
+      <c r="I33" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="B34" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C34" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D34" s="30" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E34" s="30" t="inlineStr">
+        <is>
+          <t>CREATE TRIGGER</t>
+        </is>
+      </c>
+      <c r="F34" s="30" t="inlineStr">
+        <is>
+          <t>Disparador</t>
+        </is>
+      </c>
+      <c r="G34" s="30" t="inlineStr">
+        <is>
+          <t>trg_aud_asignacion_insert</t>
+        </is>
+      </c>
+      <c r="H34" s="32" t="inlineStr">
+        <is>
+          <t>Trigger AFTER INSERT en asignacion: registra en auditoria (severidad: info)</t>
+        </is>
+      </c>
+      <c r="I34" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="34" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="B35" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C35" s="34" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D35" s="34" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E35" s="34" t="inlineStr">
+        <is>
+          <t>CREATE TRIGGER</t>
+        </is>
+      </c>
+      <c r="F35" s="34" t="inlineStr">
+        <is>
+          <t>Disparador</t>
+        </is>
+      </c>
+      <c r="G35" s="34" t="inlineStr">
+        <is>
+          <t>trg_actualizar_inscripcion_asignacion</t>
+        </is>
+      </c>
+      <c r="H35" s="37" t="inlineStr">
+        <is>
+          <t>Trigger AFTER INSERT en asignacion: inscribe automáticamente todos los alumnos del grupo</t>
+        </is>
+      </c>
+      <c r="I35" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="30" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="B36" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C36" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D36" s="30" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E36" s="30" t="inlineStr">
+        <is>
+          <t>CREATE TRIGGER</t>
+        </is>
+      </c>
+      <c r="F36" s="30" t="inlineStr">
+        <is>
+          <t>Disparador</t>
+        </is>
+      </c>
+      <c r="G36" s="30" t="inlineStr">
+        <is>
+          <t>trg_update_inscripcion_asignacion</t>
+        </is>
+      </c>
+      <c r="H36" s="32" t="inlineStr">
+        <is>
+          <t>Trigger AFTER UPDATE en asignacion: recalcula inscripciones si cambia grupo o materia</t>
+        </is>
+      </c>
+      <c r="I36" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="34" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="B37" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C37" s="34" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D37" s="34" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E37" s="34" t="inlineStr">
+        <is>
+          <t>CREATE TRIGGER</t>
+        </is>
+      </c>
+      <c r="F37" s="34" t="inlineStr">
+        <is>
+          <t>Disparador</t>
+        </is>
+      </c>
+      <c r="G37" s="34" t="inlineStr">
+        <is>
+          <t>trg_aud_asignacion_delete</t>
+        </is>
+      </c>
+      <c r="H37" s="37" t="inlineStr">
+        <is>
+          <t>Trigger AFTER DELETE en asignacion: registra en auditoria (severidad: crítico)</t>
+        </is>
+      </c>
+      <c r="I37" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="30" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="B38" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C38" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D38" s="30" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E38" s="30" t="inlineStr">
+        <is>
+          <t>CREATE TRIGGER</t>
+        </is>
+      </c>
+      <c r="F38" s="30" t="inlineStr">
+        <is>
+          <t>Disparador</t>
+        </is>
+      </c>
+      <c r="G38" s="30" t="inlineStr">
+        <is>
+          <t>trg_aud_calificacion_insert</t>
+        </is>
+      </c>
+      <c r="H38" s="32" t="inlineStr">
+        <is>
+          <t>Trigger AFTER INSERT en calificacion: registra en auditoria con datos del alumno, materia y grupo</t>
+        </is>
+      </c>
+      <c r="I38" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="34" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="B39" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C39" s="34" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D39" s="34" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E39" s="34" t="inlineStr">
+        <is>
+          <t>CREATE TRIGGER</t>
+        </is>
+      </c>
+      <c r="F39" s="34" t="inlineStr">
+        <is>
+          <t>Disparador</t>
+        </is>
+      </c>
+      <c r="G39" s="34" t="inlineStr">
+        <is>
+          <t>trg_aud_calificacion_update</t>
+        </is>
+      </c>
+      <c r="H39" s="37" t="inlineStr">
+        <is>
+          <t>Trigger AFTER UPDATE en calificacion: registra valor anterior/nuevo en auditoria (severidad: advertencia)</t>
+        </is>
+      </c>
+      <c r="I39" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="30" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="B40" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C40" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D40" s="30" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E40" s="30" t="inlineStr">
+        <is>
+          <t>CREATE TRIGGER</t>
+        </is>
+      </c>
+      <c r="F40" s="30" t="inlineStr">
+        <is>
+          <t>Disparador</t>
+        </is>
+      </c>
+      <c r="G40" s="30" t="inlineStr">
+        <is>
+          <t>trg_aud_inscripcion_insert</t>
+        </is>
+      </c>
+      <c r="H40" s="32" t="inlineStr">
+        <is>
+          <t>Trigger AFTER INSERT en inscripcion: registra alumno, materia y grupo en auditoria</t>
+        </is>
+      </c>
+      <c r="I40" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="34" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="B41" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C41" s="34" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D41" s="34" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="E41" s="34" t="inlineStr">
+        <is>
+          <t>CREATE TRIGGER</t>
+        </is>
+      </c>
+      <c r="F41" s="34" t="inlineStr">
+        <is>
+          <t>Disparador</t>
+        </is>
+      </c>
+      <c r="G41" s="34" t="inlineStr">
+        <is>
+          <t>trg_delete_calificacion_inscripcion</t>
+        </is>
+      </c>
+      <c r="H41" s="37" t="inlineStr">
+        <is>
+          <t>Trigger AFTER DELETE en inscripcion: elimina calificaciones asociadas en cascada</t>
+        </is>
+      </c>
+      <c r="I41" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="30" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="B42" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C42" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D42" s="30" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E42" s="30" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F42" s="30" t="inlineStr">
+        <is>
+          <t>Archivo PHP</t>
+        </is>
+      </c>
+      <c r="G42" s="30" t="inlineStr">
+        <is>
+          <t>config/db.php</t>
+        </is>
+      </c>
+      <c r="H42" s="32" t="inlineStr">
+        <is>
+          <t>Configuración de conexión PDO a MySQL (control_escolar_n). Define $conn global.</t>
+        </is>
+      </c>
+      <c r="I42" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="34" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="B43" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C43" s="34" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D43" s="34" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E43" s="34" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F43" s="34" t="inlineStr">
+        <is>
+          <t>Archivo PHP</t>
+        </is>
+      </c>
+      <c r="G43" s="34" t="inlineStr">
+        <is>
+          <t>session_mysql.php</t>
+        </is>
+      </c>
+      <c r="H43" s="37" t="inlineStr">
+        <is>
+          <t>Asigna @usuario y @rol como variables de sesión MySQL para uso en triggers de auditoría</t>
+        </is>
+      </c>
+      <c r="I43" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="30" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="B44" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C44" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D44" s="30" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E44" s="30" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F44" s="30" t="inlineStr">
+        <is>
+          <t>Archivo PHP</t>
+        </is>
+      </c>
+      <c r="G44" s="30" t="inlineStr">
+        <is>
+          <t>includes/auth.php</t>
+        </is>
+      </c>
+      <c r="H44" s="32" t="inlineStr">
+        <is>
+          <t>Control de acceso: verifica sesión activa y función solo() para restringir acceso por rol</t>
+        </is>
+      </c>
+      <c r="I44" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="34" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="B45" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C45" s="34" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D45" s="34" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E45" s="34" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F45" s="34" t="inlineStr">
+        <is>
+          <t>Archivo PHP</t>
+        </is>
+      </c>
+      <c r="G45" s="34" t="inlineStr">
+        <is>
+          <t>includes/funciones.php</t>
+        </is>
+      </c>
+      <c r="H45" s="37" t="inlineStr">
+        <is>
+          <t>Funciones del sistema: procesarGuardado, getAsignaciones, getAlumnosAsignacion, getBoletaAlumno, listas para selects</t>
+        </is>
+      </c>
+      <c r="I45" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="30" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="B46" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C46" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D46" s="30" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E46" s="30" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F46" s="30" t="inlineStr">
+        <is>
+          <t>Archivo PHP</t>
+        </is>
+      </c>
+      <c r="G46" s="30" t="inlineStr">
+        <is>
+          <t>includes/calificaciones.php</t>
+        </is>
+      </c>
+      <c r="H46" s="32" t="inlineStr">
+        <is>
+          <t>Archivo de inclusión para procesamiento de calificaciones vía POST</t>
+        </is>
+      </c>
+      <c r="I46" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="34" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="B47" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C47" s="34" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D47" s="34" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E47" s="34" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F47" s="34" t="inlineStr">
+        <is>
+          <t>Archivo PHP</t>
+        </is>
+      </c>
+      <c r="G47" s="34" t="inlineStr">
+        <is>
+          <t>login.php</t>
+        </is>
+      </c>
+      <c r="H47" s="37" t="inlineStr">
+        <is>
+          <t>Formulario de autenticación con redirección por rol y registro de LOGIN en auditoría</t>
+        </is>
+      </c>
+      <c r="I47" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="30" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="B48" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C48" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D48" s="30" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E48" s="30" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F48" s="30" t="inlineStr">
+        <is>
+          <t>Archivo PHP</t>
+        </is>
+      </c>
+      <c r="G48" s="30" t="inlineStr">
+        <is>
+          <t>logout.php</t>
+        </is>
+      </c>
+      <c r="H48" s="32" t="inlineStr">
+        <is>
+          <t>Cierre de sesión con registro de LOGOUT en auditoría y redirección a login.php</t>
+        </is>
+      </c>
+      <c r="I48" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="34" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="B49" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C49" s="34" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D49" s="34" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E49" s="34" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F49" s="34" t="inlineStr">
+        <is>
+          <t>Archivo PHP</t>
+        </is>
+      </c>
+      <c r="G49" s="34" t="inlineStr">
+        <is>
+          <t>dashboard.php</t>
+        </is>
+      </c>
+      <c r="H49" s="37" t="inlineStr">
+        <is>
+          <t>Panel de control con tarjetas de acceso rápido según rol (control/docente/alumno)</t>
+        </is>
+      </c>
+      <c r="I49" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="30" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="B50" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C50" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D50" s="30" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E50" s="30" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F50" s="30" t="inlineStr">
+        <is>
+          <t>Archivo PHP</t>
+        </is>
+      </c>
+      <c r="G50" s="30" t="inlineStr">
+        <is>
+          <t>index.php</t>
+        </is>
+      </c>
+      <c r="H50" s="32" t="inlineStr">
+        <is>
+          <t>Módulo de captura de calificaciones por parcial, exclusivo para rol docente</t>
+        </is>
+      </c>
+      <c r="I50" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="34" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="B51" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C51" s="34" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D51" s="34" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E51" s="34" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F51" s="34" t="inlineStr">
+        <is>
+          <t>Archivo PHP</t>
+        </is>
+      </c>
+      <c r="G51" s="34" t="inlineStr">
+        <is>
+          <t>admin.php</t>
+        </is>
+      </c>
+      <c r="H51" s="37" t="inlineStr">
+        <is>
+          <t>Módulo de gestión académica: alumnos, docentes y asignaciones (rol control)</t>
+        </is>
+      </c>
+      <c r="I51" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="30" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="B52" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C52" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D52" s="30" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E52" s="30" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F52" s="30" t="inlineStr">
+        <is>
+          <t>Archivo PHP</t>
+        </is>
+      </c>
+      <c r="G52" s="30" t="inlineStr">
+        <is>
+          <t>auditoria.php</t>
+        </is>
+      </c>
+      <c r="H52" s="32" t="inlineStr">
+        <is>
+          <t>Módulo de auditoría: visualización de todos los eventos del sistema (rol control)</t>
+        </is>
+      </c>
+      <c r="I52" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="28" customHeight="1">
+      <c r="A53" s="34" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="B53" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C53" s="34" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D53" s="34" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E53" s="34" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F53" s="34" t="inlineStr">
+        <is>
+          <t>Archivo PHP</t>
+        </is>
+      </c>
+      <c r="G53" s="34" t="inlineStr">
+        <is>
+          <t>boleta.php</t>
+        </is>
+      </c>
+      <c r="H53" s="37" t="inlineStr">
+        <is>
+          <t>Boleta de calificaciones del alumno con QR de validación digital y descarga PDF</t>
+        </is>
+      </c>
+      <c r="I53" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="30" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="B54" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C54" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D54" s="30" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E54" s="30" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F54" s="30" t="inlineStr">
+        <is>
+          <t>Archivo PHP</t>
+        </is>
+      </c>
+      <c r="G54" s="30" t="inlineStr">
+        <is>
+          <t>visualizar_calificaciones.php</t>
+        </is>
+      </c>
+      <c r="H54" s="32" t="inlineStr">
+        <is>
+          <t>Visualización de calificaciones de todas las asignaciones, exclusivo para rol control</t>
+        </is>
+      </c>
+      <c r="I54" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="34" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="B55" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C55" s="34" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D55" s="34" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E55" s="34" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F55" s="34" t="inlineStr">
+        <is>
+          <t>Archivo PHP</t>
+        </is>
+      </c>
+      <c r="G55" s="34" t="inlineStr">
+        <is>
+          <t>validar_boleta.php</t>
+        </is>
+      </c>
+      <c r="H55" s="37" t="inlineStr">
+        <is>
+          <t>Validación de autenticidad de boleta mediante folio + hash SHA-256 desde QR</t>
+        </is>
+      </c>
+      <c r="I55" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="28" customHeight="1">
+      <c r="A56" s="30" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="B56" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C56" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D56" s="30" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E56" s="30" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F56" s="30" t="inlineStr">
+        <is>
+          <t>Archivo PHP (AJAX)</t>
+        </is>
+      </c>
+      <c r="G56" s="30" t="inlineStr">
+        <is>
+          <t>ajax_editar.php</t>
+        </is>
+      </c>
+      <c r="H56" s="32" t="inlineStr">
+        <is>
+          <t>Endpoint AJAX para CRUD de alumnos, docentes y asignaciones. Genera matrícula automática.</t>
+        </is>
+      </c>
+      <c r="I56" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="34" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="B57" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C57" s="34" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D57" s="34" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E57" s="34" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F57" s="34" t="inlineStr">
+        <is>
+          <t>Archivo PHP (AJAX)</t>
+        </is>
+      </c>
+      <c r="G57" s="34" t="inlineStr">
+        <is>
+          <t>ajax_editar_asignacion.php</t>
+        </is>
+      </c>
+      <c r="H57" s="37" t="inlineStr">
+        <is>
+          <t>Endpoint AJAX para INSERT/UPDATE de asignaciones con validación de duplicados y transacciones</t>
+        </is>
+      </c>
+      <c r="I57" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="30" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="B58" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C58" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D58" s="30" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E58" s="30" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F58" s="30" t="inlineStr">
+        <is>
+          <t>Archivo PHP (AJAX)</t>
+        </is>
+      </c>
+      <c r="G58" s="30" t="inlineStr">
+        <is>
+          <t>ajax_filtros.php</t>
+        </is>
+      </c>
+      <c r="H58" s="32" t="inlineStr">
+        <is>
+          <t>Endpoint AJAX para filtros dinámicos: grupos por carrera, materias disponibles con mapa inteligente por grado</t>
+        </is>
+      </c>
+      <c r="I58" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="28" customHeight="1">
+      <c r="A59" s="34" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="B59" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C59" s="34" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D59" s="34" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E59" s="34" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F59" s="34" t="inlineStr">
+        <is>
+          <t>Archivo PHP (AJAX)</t>
+        </is>
+      </c>
+      <c r="G59" s="34" t="inlineStr">
+        <is>
+          <t>ajax_get_grupos.php</t>
+        </is>
+      </c>
+      <c r="H59" s="37" t="inlineStr">
+        <is>
+          <t>Endpoint AJAX para obtener grupos filtrados por carrera (GET)</t>
+        </is>
+      </c>
+      <c r="I59" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="28" customHeight="1">
+      <c r="A60" s="30" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="B60" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C60" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D60" s="30" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E60" s="30" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F60" s="30" t="inlineStr">
+        <is>
+          <t>Archivo PHP (AJAX)</t>
+        </is>
+      </c>
+      <c r="G60" s="30" t="inlineStr">
+        <is>
+          <t>ajax_get_materias.php</t>
+        </is>
+      </c>
+      <c r="H60" s="32" t="inlineStr">
+        <is>
+          <t>Endpoint AJAX para obtener materias filtradas por carrera y grado del grupo</t>
+        </is>
+      </c>
+      <c r="I60" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="28" customHeight="1">
+      <c r="A61" s="34" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="B61" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C61" s="34" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D61" s="34" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E61" s="34" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F61" s="34" t="inlineStr">
+        <is>
+          <t>Archivo PHP (AJAX)</t>
+        </is>
+      </c>
+      <c r="G61" s="34" t="inlineStr">
+        <is>
+          <t>ajax_get_matricula.php</t>
+        </is>
+      </c>
+      <c r="H61" s="37" t="inlineStr">
+        <is>
+          <t>Endpoint AJAX para obtener la siguiente matrícula disponible (formato A000)</t>
+        </is>
+      </c>
+      <c r="I61" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="28" customHeight="1">
+      <c r="A62" s="30" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="B62" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C62" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D62" s="30" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E62" s="30" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F62" s="30" t="inlineStr">
+        <is>
+          <t>Archivo PHP (AJAX)</t>
+        </is>
+      </c>
+      <c r="G62" s="30" t="inlineStr">
+        <is>
+          <t>ajax_listar_asignaciones.php</t>
+        </is>
+      </c>
+      <c r="H62" s="32" t="inlineStr">
+        <is>
+          <t>Endpoint AJAX para listar asignaciones en tabla HTML con botones de editar/eliminar</t>
+        </is>
+      </c>
+      <c r="I62" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="28" customHeight="1">
+      <c r="A63" s="34" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="B63" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C63" s="34" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D63" s="34" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E63" s="34" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F63" s="34" t="inlineStr">
+        <is>
+          <t>Archivo PHP (Layout)</t>
+        </is>
+      </c>
+      <c r="G63" s="34" t="inlineStr">
+        <is>
+          <t>layout/header.php</t>
+        </is>
+      </c>
+      <c r="H63" s="37" t="inlineStr">
+        <is>
+          <t>Cabecera HTML global: Bootstrap, DataTables, navbar responsiva con opciones por rol</t>
+        </is>
+      </c>
+      <c r="I63" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="30" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="B64" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C64" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D64" s="30" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E64" s="30" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F64" s="30" t="inlineStr">
+        <is>
+          <t>Archivo PHP (Layout)</t>
+        </is>
+      </c>
+      <c r="G64" s="30" t="inlineStr">
+        <is>
+          <t>layout/footer.php</t>
+        </is>
+      </c>
+      <c r="H64" s="32" t="inlineStr">
+        <is>
+          <t>Pie de página global: scripts jQuery, Bootstrap, footer con copyright</t>
+        </is>
+      </c>
+      <c r="I64" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="28" customHeight="1">
+      <c r="A65" s="34" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="B65" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C65" s="34" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D65" s="34" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E65" s="34" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F65" s="34" t="inlineStr">
+        <is>
+          <t>Archivo JavaScript</t>
+        </is>
+      </c>
+      <c r="G65" s="34" t="inlineStr">
+        <is>
+          <t>assets/js/calificaciones.js</t>
+        </is>
+      </c>
+      <c r="H65" s="37" t="inlineStr">
+        <is>
+          <t>Cálculo en tiempo real de promedio y estado (Aprobado/Reprobado/Baja asistencia). Validación rango 0-10.</t>
+        </is>
+      </c>
+      <c r="I65" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="28" customHeight="1">
+      <c r="A66" s="30" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="B66" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C66" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D66" s="30" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E66" s="30" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F66" s="30" t="inlineStr">
+        <is>
+          <t>Archivo JavaScript</t>
+        </is>
+      </c>
+      <c r="G66" s="30" t="inlineStr">
+        <is>
+          <t>assets/js/validaciones.js</t>
+        </is>
+      </c>
+      <c r="H66" s="32" t="inlineStr">
+        <is>
+          <t>Validaciones globales: nombre completo, correo, matrícula (regex A000), formularios de alumnos/docentes/asignaciones</t>
+        </is>
+      </c>
+      <c r="I66" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="28" customHeight="1">
+      <c r="A67" s="34" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="B67" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C67" s="34" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D67" s="34" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E67" s="34" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F67" s="34" t="inlineStr">
+        <is>
+          <t>Archivo JavaScript</t>
+        </is>
+      </c>
+      <c r="G67" s="34" t="inlineStr">
+        <is>
+          <t>assets/js/responsive.js</t>
+        </is>
+      </c>
+      <c r="H67" s="37" t="inlineStr">
+        <is>
+          <t>Manejo responsivo con accordion: muestra/oculta secciones en móvil con animación slideToggle</t>
+        </is>
+      </c>
+      <c r="I67" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="28" customHeight="1">
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="B68" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>Archivo JavaScript</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>assets/js/accordion-mobile.js</t>
+        </is>
+      </c>
+      <c r="H68" s="32" t="inlineStr">
+        <is>
+          <t>Accordion exclusivo para móvil: abre/cierra secciones .seccion-movil en pantallas &lt; 768px</t>
+        </is>
+      </c>
+      <c r="I68" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="34" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="B69" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C69" s="34" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D69" s="34" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E69" s="34" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F69" s="34" t="inlineStr">
+        <is>
+          <t>Archivo JavaScript</t>
+        </is>
+      </c>
+      <c r="G69" s="34" t="inlineStr">
+        <is>
+          <t>assets/js/cards.js</t>
+        </is>
+      </c>
+      <c r="H69" s="37" t="inlineStr">
+        <is>
+          <t>Convierte tablas .tabla-card en tarjetas Bootstrap para visualización móvil</t>
+        </is>
+      </c>
+      <c r="I69" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="28" customHeight="1">
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="B70" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C70" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D70" s="30" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E70" s="30" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F70" s="30" t="inlineStr">
+        <is>
+          <t>Archivo CSS</t>
+        </is>
+      </c>
+      <c r="G70" s="30" t="inlineStr">
+        <is>
+          <t>assets/css/captura.css</t>
+        </is>
+      </c>
+      <c r="H70" s="32" t="inlineStr">
+        <is>
+          <t>Estilos principales del módulo de captura: variables de color, card, tabla, inputs, badges de estado</t>
+        </is>
+      </c>
+      <c r="I70" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="28" customHeight="1">
+      <c r="A71" s="34" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="B71" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C71" s="34" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D71" s="34" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E71" s="34" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F71" s="34" t="inlineStr">
+        <is>
+          <t>Archivo CSS</t>
+        </is>
+      </c>
+      <c r="G71" s="34" t="inlineStr">
+        <is>
+          <t>assets/css/accordion.css</t>
+        </is>
+      </c>
+      <c r="H71" s="37" t="inlineStr">
+        <is>
+          <t>Estilos del accordion responsivo para móvil (max-width 768px)</t>
+        </is>
+      </c>
+      <c r="I71" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="28" customHeight="1">
+      <c r="A72" s="30" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="B72" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C72" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D72" s="30" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E72" s="30" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F72" s="30" t="inlineStr">
+        <is>
+          <t>Archivo CSS</t>
+        </is>
+      </c>
+      <c r="G72" s="30" t="inlineStr">
+        <is>
+          <t>assets/css/cards.css</t>
+        </is>
+      </c>
+      <c r="H72" s="32" t="inlineStr">
+        <is>
+          <t>Estilos de tarjetas Bootstrap para visualización de tablas en móvil</t>
+        </is>
+      </c>
+      <c r="I72" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="28" customHeight="1">
+      <c r="A73" s="34" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="B73" s="40" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C73" s="34" t="inlineStr">
+        <is>
+          <t>Jorge Sebastian</t>
+        </is>
+      </c>
+      <c r="D73" s="34" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E73" s="34" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F73" s="34" t="inlineStr">
+        <is>
+          <t>Archivo CSS</t>
+        </is>
+      </c>
+      <c r="G73" s="34" t="inlineStr">
+        <is>
+          <t>assets/css/responsive.css</t>
+        </is>
+      </c>
+      <c r="H73" s="37" t="inlineStr">
+        <is>
+          <t>Estilos responsivos globales: fuentes, bordes redondeados, altura de inputs, overflow-x hidden</t>
+        </is>
+      </c>
+      <c r="I73" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="28" customHeight="1">
+      <c r="A74" s="30" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="B74" s="39" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C74" s="30" t="inlineStr">
+        <is>
+          <t>Jose Emiliano</t>
+        </is>
+      </c>
+      <c r="D74" s="30" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="E74" s="30" t="inlineStr">
+        <is>
+          <t>CREATE FILE</t>
+        </is>
+      </c>
+      <c r="F74" s="30" t="inlineStr">
+        <is>
+          <t>Imagen</t>
+        </is>
+      </c>
+      <c r="G74" s="30" t="inlineStr">
+        <is>
+          <t>img/logo.png</t>
+        </is>
+      </c>
+      <c r="H74" s="32" t="inlineStr">
+        <is>
+          <t>Logotipo del Sistema Escolar SE (birrete con marco azul) utilizado en navbar y boleta PDF</t>
+        </is>
+      </c>
+      <c r="I74" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
       </c>
     </row>
   </sheetData>
